--- a/InputData/trans/BPHEVSP/BAU PHEV Subsidy Perc.xlsx
+++ b/InputData/trans/BPHEVSP/BAU PHEV Subsidy Perc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobrien\Dropbox (Energy Innovation)\Desktop\Models\State Models\eps-newmexico\InputData\trans\BPHEVSP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A447AC0A-1BDC-44C3-A322-1E528C4B4897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9278062-3461-4103-9EB9-13BFD56CE94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31965" yWindow="2160" windowWidth="24480" windowHeight="13800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="59640" yWindow="1380" windowWidth="24615" windowHeight="15060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
